--- a/input/excel/Profil and ValueSet_ AllergyIntolerance_18.08.2025_v4/VerificationStatusVS.xlsx
+++ b/input/excel/Profil and ValueSet_ AllergyIntolerance_18.08.2025_v4/VerificationStatusVS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\behzod_axmedov\Desktop\DHP-temp02\DHP-temp\input\excel\Profil and ValueSet_ AllergyIntolerance_18.08.2025_v4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\behzod_axmedov\Desktop\DHP-temp02\Aller_DHP\digital-health-ig\input\excel\Profil and ValueSet_ AllergyIntolerance_18.08.2025_v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D41215D9-3166-4F13-A9B6-FD674BEE5BED}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30620669-C2D3-44E8-AE3C-94B663D0DE48}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3540" yWindow="2280" windowWidth="22440" windowHeight="13155" xr2:uid="{FB043A6A-4D0B-4EB9-B6F5-D6E60EEB5BD3}"/>
+    <workbookView xWindow="14430" yWindow="1650" windowWidth="12615" windowHeight="10230" xr2:uid="{FB043A6A-4D0B-4EB9-B6F5-D6E60EEB5BD3}"/>
   </bookViews>
   <sheets>
     <sheet name="VerificationStatusVS" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>CODE</t>
   </si>
@@ -112,6 +112,18 @@
   </si>
   <si>
     <t>Информация ошибочна, должна быть удалена из учёта.</t>
+  </si>
+  <si>
+    <t>presumed</t>
+  </si>
+  <si>
+    <t>Taxmin qilingan</t>
+  </si>
+  <si>
+    <t>Предполагаемый</t>
+  </si>
+  <si>
+    <t>Presumed</t>
   </si>
 </sst>
 </file>
@@ -559,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD50C133-92FB-4D81-B49A-C761B5827915}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
@@ -570,7 +582,7 @@
     <col min="6" max="6" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -610,63 +622,79 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="E3" s="4"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:6" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F6" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="F2:F6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{BDD2EAE1-1E70-42D0-8BBE-F1EA5AEA92C8}"/>
